--- a/Projects/MISQ/MISQ round 2/analysis/outputs/explore260525_AISimWithXXX_summarization (add 1Ans and handle anchor).xlsx
+++ b/Projects/MISQ/MISQ round 2/analysis/outputs/explore260525_AISimWithXXX_summarization (add 1Ans and handle anchor).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dylanchen/Desktop/geek-community/Projects/MISQ/MISQ round 2/analysis/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B499100D-8538-F34F-A392-DD399C413B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8765ADFC-3A81-0745-9C3B-416AC38A1FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19540" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
   </bookViews>
@@ -494,11 +494,6 @@
     <t>(0.021)</t>
   </si>
   <si>
-    <t>AI+AI:Sim w/ Accept (fillNA)
-Setup 1
-- experience/insight/alternative样本限制在first human answer</t>
-  </si>
-  <si>
     <t>AI+AI:Sim w/ Opus (fillNA)
 Setup 1</t>
   </si>
@@ -794,33 +789,92 @@
     <t>247</t>
   </si>
   <si>
-    <t>AI+AI:Sim w/ Accept (fillNA)
+    <r>
+      <t xml:space="preserve">AI+AI:Sim w/ Accept (fillNA)
+Setup 1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>- 对于LLM quality DV：如果这个样本本身就是accepted/most like，剔除
+- 对于human1_human2_similarity，如果计算DV涉及到accepted/most like的answer，剔除</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI+AI:Sim w/ Accept (fillNA)
 Setup 2
-- 对于LLM quality DV：如果这个样本本身就是accepted/most like，剔除
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>- 对于LLM quality DV：如果这个样本本身就是accepted/most like，剔除
 - 对于answer1_answer2_similarity，如果计算DV涉及到accepted/most like的answer，剔除</t>
-  </si>
-  <si>
-    <t>AI+AI:Sim w/ Accept (fillNA)
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI+AI:Sim w/ Accept (fillNA)
 Setup 1
-- 对于LLM quality DV：如果这个样本本身就是accepted/most like，剔除
-- 对于human1_human2_similarity，如果计算DV涉及到accepted/most like的answer，剔除</t>
-  </si>
-  <si>
-    <t>AI+AI:Sim w/ Accept (fillNA)
+- experience/insight/alternative样本限制在first human answer
+p.s. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>现在的样本如果涉及accepted/most like，没有剔除。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI+AI:Sim w/ Accept (fillNA)
 Setup 2
 - contribution DV变成# other answer，也就是control里面从第二个human开始计数。所以treatment正向显著
 - experience/insight/alternative样本限制在second answer
-p.s. 现在的交互是first answer的质量（可以是AI也可以是人）</t>
+p.s. 现在的交互是first answer的质量（可以是AI也可以是人）
+p.s. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>现在的样本如果涉及accepted/most like，没有剔除。</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -896,7 +950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -906,12 +960,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -919,6 +967,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1281,18 +1338,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="7" t="s">
-        <v>151</v>
+      <c r="B2" s="5" t="s">
+        <v>250</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="9"/>
+      <c r="G2" s="7"/>
       <c r="H2" s="4" t="s">
         <v>145</v>
       </c>
@@ -1302,22 +1359,22 @@
       <c r="J2" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="N2" s="7" t="s">
-        <v>250</v>
+      <c r="L2" s="7"/>
+      <c r="N2" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="O2" s="3"/>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9" t="s">
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="9"/>
+      <c r="S2" s="7"/>
       <c r="T2" s="4" t="s">
         <v>145</v>
       </c>
@@ -1327,14 +1384,14 @@
       <c r="V2" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="W2" s="9" t="s">
+      <c r="W2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="X2" s="9"/>
+      <c r="X2" s="7"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B3" s="8"/>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -1364,8 +1421,8 @@
       <c r="L3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="N3" s="8"/>
-      <c r="O3" s="5" t="s">
+      <c r="N3" s="6"/>
+      <c r="O3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="P3" s="4" t="s">
@@ -1381,24 +1438,24 @@
         <v>8</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="U3" s="4" t="s">
         <v>108</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="W3" s="4" t="s">
         <v>122</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B4" s="8"/>
-      <c r="C4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="4" t="s">
         <v>21</v>
       </c>
@@ -1426,8 +1483,8 @@
       <c r="L4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="8"/>
-      <c r="O4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="9"/>
       <c r="P4" s="4" t="s">
         <v>21</v>
       </c>
@@ -1441,24 +1498,24 @@
         <v>24</v>
       </c>
       <c r="T4" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="U4" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="V4" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="W4" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="X4" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="X4" s="4" t="s">
-        <v>217</v>
-      </c>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B5" s="8"/>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="4"/>
@@ -1482,8 +1539,8 @@
       <c r="L5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="N5" s="8"/>
-      <c r="O5" s="5" t="s">
+      <c r="N5" s="6"/>
+      <c r="O5" s="8" t="s">
         <v>12</v>
       </c>
       <c r="P5" s="4"/>
@@ -1501,7 +1558,7 @@
         <v>66</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4" t="s">
@@ -1509,8 +1566,8 @@
       </c>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B6" s="8"/>
-      <c r="C6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="9"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
         <v>35</v>
@@ -1532,8 +1589,8 @@
       <c r="L6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="9"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="s">
         <v>35</v>
@@ -1549,16 +1606,16 @@
         <v>22</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="W6" s="4"/>
       <c r="X6" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B7" s="8"/>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="4"/>
@@ -1582,8 +1639,8 @@
       <c r="L7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="8"/>
-      <c r="O7" s="5" t="s">
+      <c r="N7" s="6"/>
+      <c r="O7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="P7" s="4"/>
@@ -1595,22 +1652,22 @@
         <v>42</v>
       </c>
       <c r="T7" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="U7" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="U7" s="4" t="s">
-        <v>222</v>
-      </c>
       <c r="V7" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="W7" s="4"/>
       <c r="X7" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B8" s="8"/>
-      <c r="C8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>43</v>
@@ -1632,8 +1689,8 @@
       <c r="L8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="8"/>
-      <c r="O8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="9"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4" t="s">
         <v>43</v>
@@ -1643,10 +1700,10 @@
         <v>44</v>
       </c>
       <c r="T8" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="U8" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>225</v>
       </c>
       <c r="V8" s="4" t="s">
         <v>44</v>
@@ -1657,7 +1714,7 @@
       </c>
     </row>
     <row r="9" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B9" s="8"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
@@ -1688,7 +1745,7 @@
       <c r="L9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="N9" s="8"/>
+      <c r="N9" s="6"/>
       <c r="O9" s="3" t="s">
         <v>18</v>
       </c>
@@ -1704,20 +1761,20 @@
       <c r="S9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="T9" s="4" t="s">
+      <c r="T9" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="U9" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="V9" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="W9" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="U9" s="4" t="s">
+      <c r="X9" s="10" t="s">
         <v>226</v>
-      </c>
-      <c r="V9" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.2">
@@ -1732,18 +1789,18 @@
       <c r="X10" s="2"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>251</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="9"/>
+      <c r="G11" s="7"/>
       <c r="H11" s="4" t="s">
         <v>145</v>
       </c>
@@ -1753,22 +1810,22 @@
       <c r="J11" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="N11" s="7" t="s">
+      <c r="L11" s="7"/>
+      <c r="N11" s="5" t="s">
         <v>249</v>
       </c>
       <c r="O11" s="3"/>
-      <c r="P11" s="9" t="s">
+      <c r="P11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9" t="s">
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="S11" s="9"/>
+      <c r="S11" s="7"/>
       <c r="T11" s="4" t="s">
         <v>145</v>
       </c>
@@ -1778,30 +1835,30 @@
       <c r="V11" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="W11" s="9" t="s">
+      <c r="W11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="X11" s="9"/>
+      <c r="X11" s="7"/>
     </row>
     <row r="12" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B12" s="8"/>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>149</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>9</v>
@@ -1815,52 +1872,52 @@
       <c r="L12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="N12" s="8"/>
-      <c r="O12" s="5" t="s">
+      <c r="N12" s="6"/>
+      <c r="O12" s="8" t="s">
         <v>5</v>
       </c>
       <c r="P12" s="4" t="s">
         <v>149</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T12" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="U12" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="U12" s="4" t="s">
+      <c r="V12" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="V12" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="W12" s="4" t="s">
         <v>142</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B13" s="8"/>
-      <c r="C13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>25</v>
@@ -1877,48 +1934,48 @@
       <c r="L13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="N13" s="8"/>
-      <c r="O13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="9"/>
       <c r="P13" s="4" t="s">
         <v>38</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="T13" s="4" t="s">
         <v>109</v>
       </c>
       <c r="U13" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="V13" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="W13" s="4" t="s">
         <v>118</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B14" s="8"/>
-      <c r="C14" s="5" t="s">
-        <v>159</v>
+      <c r="B14" s="6"/>
+      <c r="C14" s="8" t="s">
+        <v>158</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>86</v>
@@ -1933,42 +1990,42 @@
       <c r="L14" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="N14" s="8"/>
-      <c r="O14" s="5" t="s">
-        <v>159</v>
+      <c r="N14" s="6"/>
+      <c r="O14" s="8" t="s">
+        <v>158</v>
       </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V14" s="4" t="s">
         <v>122</v>
       </c>
       <c r="W14" s="4"/>
       <c r="X14" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B15" s="8"/>
-      <c r="C15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
         <v>150</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>37</v>
@@ -1983,15 +2040,15 @@
       <c r="L15" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="N15" s="8"/>
-      <c r="O15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="9"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4" t="s">
         <v>150</v>
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T15" s="4" t="s">
         <v>40</v>
@@ -2004,21 +2061,21 @@
       </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B16" s="8"/>
-      <c r="C16" s="5" t="s">
-        <v>170</v>
+      <c r="B16" s="6"/>
+      <c r="C16" s="8" t="s">
+        <v>169</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>15</v>
@@ -2033,38 +2090,38 @@
       <c r="L16" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="N16" s="8"/>
-      <c r="O16" s="5" t="s">
-        <v>170</v>
+      <c r="N16" s="6"/>
+      <c r="O16" s="8" t="s">
+        <v>169</v>
       </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T16" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="U16" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="U16" s="4" t="s">
+      <c r="V16" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="V16" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="W16" s="4"/>
       <c r="X16" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B17" s="8"/>
-      <c r="C17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="9"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4" t="s">
@@ -2083,32 +2140,32 @@
       <c r="L17" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="N17" s="8"/>
-      <c r="O17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="9"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4" t="s">
         <v>144</v>
       </c>
       <c r="T17" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="U17" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="U17" s="4" t="s">
+      <c r="V17" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="V17" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="W17" s="4"/>
       <c r="X17" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B18" s="8"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="3" t="s">
         <v>18</v>
       </c>
@@ -2116,13 +2173,13 @@
         <v>48</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>48</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>119</v>
@@ -2137,9 +2194,9 @@
         <v>81</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="N18" s="8"/>
+        <v>168</v>
+      </c>
+      <c r="N18" s="6"/>
       <c r="O18" s="3" t="s">
         <v>18</v>
       </c>
@@ -2147,43 +2204,43 @@
         <v>48</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R18" s="4" t="s">
         <v>48</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="T18" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="T18" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="U18" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="V18" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="W18" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="U18" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="V18" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="W18" s="4" t="s">
+      <c r="X18" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="X18" s="4" t="s">
-        <v>248</v>
-      </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B20" s="7" t="s">
-        <v>152</v>
+      <c r="B20" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9" t="s">
+      <c r="E20" s="7"/>
+      <c r="F20" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G20" s="9"/>
+      <c r="G20" s="7"/>
       <c r="H20" s="4" t="s">
         <v>145</v>
       </c>
@@ -2193,14 +2250,14 @@
       <c r="J20" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L20" s="9"/>
+      <c r="L20" s="7"/>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B21" s="8"/>
-      <c r="C21" s="5" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="4" t="s">
@@ -2232,8 +2289,8 @@
       </c>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B22" s="8"/>
-      <c r="C22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="9"/>
       <c r="D22" s="4" t="s">
         <v>21</v>
       </c>
@@ -2263,8 +2320,8 @@
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B23" s="8"/>
-      <c r="C23" s="5" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="4"/>
@@ -2290,8 +2347,8 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B24" s="8"/>
-      <c r="C24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="9"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
         <v>35</v>
@@ -2315,8 +2372,8 @@
       </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B25" s="8"/>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D25" s="4"/>
@@ -2342,8 +2399,8 @@
       </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B26" s="8"/>
-      <c r="C26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="9"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
         <v>100</v>
@@ -2367,7 +2424,7 @@
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B27" s="8"/>
+      <c r="B27" s="6"/>
       <c r="C27" s="3" t="s">
         <v>18</v>
       </c>
@@ -2400,18 +2457,18 @@
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B29" s="7" t="s">
-        <v>153</v>
+      <c r="B29" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="C29" s="3"/>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9" t="s">
+      <c r="E29" s="7"/>
+      <c r="F29" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G29" s="9"/>
+      <c r="G29" s="7"/>
       <c r="H29" s="4" t="s">
         <v>145</v>
       </c>
@@ -2421,30 +2478,30 @@
       <c r="J29" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="K29" s="9" t="s">
+      <c r="K29" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L29" s="9"/>
+      <c r="L29" s="7"/>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B30" s="8"/>
-      <c r="C30" s="5" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>149</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G30" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>129</v>
@@ -2456,23 +2513,23 @@
         <v>74</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B31" s="8"/>
-      <c r="C31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="9"/>
       <c r="D31" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>110</v>
@@ -2491,17 +2548,17 @@
       </c>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B32" s="8"/>
-      <c r="C32" s="5" t="s">
-        <v>159</v>
+      <c r="B32" s="6"/>
+      <c r="C32" s="8" t="s">
+        <v>158</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>129</v>
@@ -2510,7 +2567,7 @@
         <v>66</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4" t="s">
@@ -2518,11 +2575,11 @@
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="8"/>
-      <c r="C33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="9"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4" t="s">
@@ -2543,42 +2600,42 @@
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="8"/>
-      <c r="C34" s="5" t="s">
-        <v>201</v>
+      <c r="B34" s="6"/>
+      <c r="C34" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4" t="s">
         <v>114</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>51</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="8"/>
-      <c r="C35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="9"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>137</v>
@@ -2595,7 +2652,7 @@
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B36" s="8"/>
+      <c r="B36" s="6"/>
       <c r="C36" s="3" t="s">
         <v>18</v>
       </c>
@@ -2603,43 +2660,43 @@
         <v>48</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>48</v>
       </c>
       <c r="G36" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H36" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>207</v>
-      </c>
       <c r="I36" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>81</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B38" s="7" t="s">
-        <v>154</v>
+      <c r="B38" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9" t="s">
+      <c r="E38" s="7"/>
+      <c r="F38" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G38" s="9"/>
+      <c r="G38" s="7"/>
       <c r="H38" s="4" t="s">
         <v>145</v>
       </c>
@@ -2649,14 +2706,14 @@
       <c r="J38" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="K38" s="9" t="s">
+      <c r="K38" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L38" s="9"/>
+      <c r="L38" s="7"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B39" s="8"/>
-      <c r="C39" s="5" t="s">
+      <c r="B39" s="6"/>
+      <c r="C39" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D39" s="4" t="s">
@@ -2688,8 +2745,8 @@
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B40" s="8"/>
-      <c r="C40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="9"/>
       <c r="D40" s="4" t="s">
         <v>21</v>
       </c>
@@ -2719,8 +2776,8 @@
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B41" s="8"/>
-      <c r="C41" s="5" t="s">
+      <c r="B41" s="6"/>
+      <c r="C41" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D41" s="4"/>
@@ -2746,8 +2803,8 @@
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B42" s="8"/>
-      <c r="C42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="9"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4" t="s">
         <v>35</v>
@@ -2771,8 +2828,8 @@
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B43" s="8"/>
-      <c r="C43" s="5" t="s">
+      <c r="B43" s="6"/>
+      <c r="C43" s="8" t="s">
         <v>130</v>
       </c>
       <c r="D43" s="4"/>
@@ -2798,8 +2855,8 @@
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B44" s="8"/>
-      <c r="C44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="9"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
         <v>135</v>
@@ -2823,7 +2880,7 @@
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B45" s="8"/>
+      <c r="B45" s="6"/>
       <c r="C45" s="3" t="s">
         <v>18</v>
       </c>
@@ -2856,18 +2913,18 @@
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B47" s="7" t="s">
-        <v>155</v>
+      <c r="B47" s="5" t="s">
+        <v>154</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9" t="s">
+      <c r="E47" s="7"/>
+      <c r="F47" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="9"/>
+      <c r="G47" s="7"/>
       <c r="H47" s="4" t="s">
         <v>145</v>
       </c>
@@ -2877,52 +2934,52 @@
       <c r="J47" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="K47" s="9" t="s">
+      <c r="K47" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L47" s="9"/>
+      <c r="L47" s="7"/>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B48" s="8"/>
-      <c r="C48" s="5" t="s">
+      <c r="B48" s="6"/>
+      <c r="C48" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>149</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G48" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H48" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>74</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B49" s="8"/>
-      <c r="C49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="9"/>
       <c r="D49" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>31</v>
@@ -2947,17 +3004,17 @@
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B50" s="8"/>
-      <c r="C50" s="5" t="s">
-        <v>159</v>
+      <c r="B50" s="6"/>
+      <c r="C50" s="8" t="s">
+        <v>158</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>129</v>
@@ -2970,19 +3027,19 @@
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B51" s="8"/>
-      <c r="C51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="9"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>67</v>
@@ -2999,42 +3056,42 @@
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B52" s="8"/>
-      <c r="C52" s="5" t="s">
-        <v>182</v>
+      <c r="B52" s="6"/>
+      <c r="C52" s="8" t="s">
+        <v>181</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I52" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="H52" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="I52" s="4" t="s">
+      <c r="J52" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B53" s="8"/>
-      <c r="C53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="9"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>116</v>
@@ -3051,7 +3108,7 @@
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B54" s="8"/>
+      <c r="B54" s="6"/>
       <c r="C54" s="3" t="s">
         <v>18</v>
       </c>
@@ -3059,70 +3116,32 @@
         <v>48</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>48</v>
       </c>
       <c r="G54" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H54" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="H54" s="4" t="s">
-        <v>191</v>
-      </c>
       <c r="I54" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>81</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="N11:N18"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="O12:O13"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="N2:N9"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="B47:B54"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="B11:B18"/>
-    <mergeCell ref="B20:B27"/>
-    <mergeCell ref="B29:B36"/>
-    <mergeCell ref="B38:B45"/>
     <mergeCell ref="C34:C35"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
@@ -3135,12 +3154,50 @@
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="B11:B18"/>
+    <mergeCell ref="B20:B27"/>
+    <mergeCell ref="B29:B36"/>
+    <mergeCell ref="B38:B45"/>
+    <mergeCell ref="B47:B54"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="K47:L47"/>
     <mergeCell ref="C48:C49"/>
     <mergeCell ref="C50:C51"/>
     <mergeCell ref="C52:C53"/>
     <mergeCell ref="C39:C40"/>
     <mergeCell ref="C41:C42"/>
     <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="N2:N9"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="N11:N18"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="O16:O17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
